--- a/docs/VP地址规划.xlsx
+++ b/docs/VP地址规划.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Template4T5L\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12540"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="192">
   <si>
     <t>设备</t>
   </si>
@@ -22,9 +27,6 @@
     <t>vp地址</t>
   </si>
   <si>
-    <t>大小(字)</t>
-  </si>
-  <si>
     <t>1字</t>
   </si>
   <si>
@@ -127,9 +129,6 @@
     <t>锁</t>
   </si>
   <si>
-    <t>0x5125</t>
-  </si>
-  <si>
     <t>蓝牙状态</t>
   </si>
   <si>
@@ -178,707 +177,560 @@
     <t>0x3002</t>
   </si>
   <si>
+    <t>screen_mode</t>
+  </si>
+  <si>
+    <t>0x3003</t>
+  </si>
+  <si>
+    <t>1=屏保，2=息屏</t>
+  </si>
+  <si>
+    <t>volume_percent</t>
+  </si>
+  <si>
+    <t>0x3004</t>
+  </si>
+  <si>
+    <t>language</t>
+  </si>
+  <si>
+    <t>0x3005</t>
+  </si>
+  <si>
+    <t>1=中；2=英；3=韩；4=日</t>
+  </si>
+  <si>
+    <t>local_password_enabled</t>
+  </si>
+  <si>
+    <t>0x3006</t>
+  </si>
+  <si>
+    <t>0x3007</t>
+  </si>
+  <si>
+    <t>0x3008</t>
+  </si>
+  <si>
+    <t>0x3009</t>
+  </si>
+  <si>
+    <t>0x300A</t>
+  </si>
+  <si>
+    <t>0x300B</t>
+  </si>
+  <si>
+    <t>0x300C</t>
+  </si>
+  <si>
+    <t>0x300D</t>
+  </si>
+  <si>
+    <t>0x300E-0x300F</t>
+  </si>
+  <si>
+    <t>temperature</t>
+  </si>
+  <si>
+    <t>0x3010-0x3011</t>
+  </si>
+  <si>
+    <t>double(4字节)</t>
+  </si>
+  <si>
+    <t>humidity</t>
+  </si>
+  <si>
+    <t>0x3012</t>
+  </si>
+  <si>
+    <t>pm25</t>
+  </si>
+  <si>
+    <t>0x3013-0x3014</t>
+  </si>
+  <si>
+    <t>co2</t>
+  </si>
+  <si>
+    <t>0x3015-0x3016</t>
+  </si>
+  <si>
+    <t>0x3017</t>
+  </si>
+  <si>
+    <t>door_status</t>
+  </si>
+  <si>
+    <t>0x3018</t>
+  </si>
+  <si>
+    <t>0x00=CLOSED；0x01=OPEN</t>
+  </si>
+  <si>
+    <t>lock_status</t>
+  </si>
+  <si>
+    <t>0x3019</t>
+  </si>
+  <si>
+    <t>0x00=LOCKED；0x01=UNLOCKED</t>
+  </si>
+  <si>
+    <t>exhaust-enabled</t>
+  </si>
+  <si>
+    <t>0x301A</t>
+  </si>
+  <si>
+    <t>0x00=false；0x01=true</t>
+  </si>
+  <si>
+    <t>exhaust-speed_level</t>
+  </si>
+  <si>
+    <t>0x301B</t>
+  </si>
+  <si>
+    <t>0x1，0x2，0x3，0x4，0x5，0x6</t>
+  </si>
+  <si>
+    <t>exhaust-interval_hours</t>
+  </si>
+  <si>
+    <t>0x301C</t>
+  </si>
+  <si>
+    <t>exhaust-running</t>
+  </si>
+  <si>
+    <t>0x301D</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>0x301E</t>
+  </si>
+  <si>
+    <t>light-enabled</t>
+  </si>
+  <si>
+    <t>0x301F</t>
+  </si>
+  <si>
+    <t>light-brightness_level</t>
+  </si>
+  <si>
+    <t>0x3020</t>
+  </si>
+  <si>
+    <t>0x1，0x2，0x3，0x4</t>
+  </si>
+  <si>
+    <t>light-running</t>
+  </si>
+  <si>
+    <t>0x3021</t>
+  </si>
+  <si>
+    <t>0x3022</t>
+  </si>
+  <si>
+    <t>0x3023</t>
+  </si>
+  <si>
+    <t>uvb-enabled</t>
+  </si>
+  <si>
+    <t>0x3024</t>
+  </si>
+  <si>
+    <t>uvb-level</t>
+  </si>
+  <si>
+    <t>0x3025</t>
+  </si>
+  <si>
+    <t>uvb-daily_hours</t>
+  </si>
+  <si>
+    <t>0x3026</t>
+  </si>
+  <si>
+    <t>uvb-running</t>
+  </si>
+  <si>
+    <t>0x3027</t>
+  </si>
+  <si>
+    <t>uvb-null</t>
+  </si>
+  <si>
+    <t>0x3028</t>
+  </si>
+  <si>
+    <t>anion-enabled</t>
+  </si>
+  <si>
+    <t>0x3029</t>
+  </si>
+  <si>
+    <t>anion-running</t>
+  </si>
+  <si>
+    <t>0x302A</t>
+  </si>
+  <si>
+    <t>anion</t>
+  </si>
+  <si>
+    <t>0x302B</t>
+  </si>
+  <si>
+    <t>0x302C</t>
+  </si>
+  <si>
+    <t>0x302D</t>
+  </si>
+  <si>
+    <t>plasma-enabled</t>
+  </si>
+  <si>
+    <t>0x302E</t>
+  </si>
+  <si>
+    <t>plasma-running</t>
+  </si>
+  <si>
+    <t>0x302F</t>
+  </si>
+  <si>
+    <t>plasma</t>
+  </si>
+  <si>
+    <t>0x3030</t>
+  </si>
+  <si>
+    <t>0x3031</t>
+  </si>
+  <si>
+    <t>0x3032</t>
+  </si>
+  <si>
+    <t>climate-enabled</t>
+  </si>
+  <si>
+    <t>0x3033</t>
+  </si>
+  <si>
+    <t>climate-target_celsius</t>
+  </si>
+  <si>
+    <t>0x3034</t>
+  </si>
+  <si>
+    <t>20-35</t>
+  </si>
+  <si>
+    <t>climate-control_status</t>
+  </si>
+  <si>
+    <t>0x3035</t>
+  </si>
+  <si>
+    <t>climate-running</t>
+  </si>
+  <si>
+    <t>0x3036</t>
+  </si>
+  <si>
+    <t>climate</t>
+  </si>
+  <si>
+    <t>0x3037</t>
+  </si>
+  <si>
+    <t>humidifier-enabled</t>
+  </si>
+  <si>
+    <t>0x3038</t>
+  </si>
+  <si>
+    <t>humidifier-interval_hours</t>
+  </si>
+  <si>
+    <t>0x3039</t>
+  </si>
+  <si>
+    <t>humidifier-running_hours</t>
+  </si>
+  <si>
+    <t>0x303A</t>
+  </si>
+  <si>
+    <t>humidifier-running</t>
+  </si>
+  <si>
+    <t>0x303B</t>
+  </si>
+  <si>
+    <t>humidifier-liquid_status</t>
+  </si>
+  <si>
+    <t>0x303C</t>
+  </si>
+  <si>
+    <t>inlet_fan-enabled</t>
+  </si>
+  <si>
+    <t>0x303D</t>
+  </si>
+  <si>
+    <t>inlet_fan-speed_level</t>
+  </si>
+  <si>
+    <t>0x303E</t>
+  </si>
+  <si>
+    <t>0x1,0x2,0x3,0x4</t>
+  </si>
+  <si>
+    <t>inlet_fan-running</t>
+  </si>
+  <si>
+    <t>0x303F</t>
+  </si>
+  <si>
+    <t>inlet_fan-</t>
+  </si>
+  <si>
+    <t>0x3040</t>
+  </si>
+  <si>
+    <t>0x3041</t>
+  </si>
+  <si>
+    <t>filter-life_percent</t>
+  </si>
+  <si>
+    <t>0x3042</t>
+  </si>
+  <si>
+    <t>filter-need_replace</t>
+  </si>
+  <si>
+    <t>0x3043</t>
+  </si>
+  <si>
+    <t>filter-</t>
+  </si>
+  <si>
+    <t>0x3044</t>
+  </si>
+  <si>
+    <t>0x3045</t>
+  </si>
+  <si>
+    <t>0x3046</t>
+  </si>
+  <si>
+    <t>0x3047</t>
+  </si>
+  <si>
+    <t>0x3048</t>
+  </si>
+  <si>
+    <t>0x3049</t>
+  </si>
+  <si>
+    <t>0x304A</t>
+  </si>
+  <si>
+    <t>0x304B</t>
+  </si>
+  <si>
+    <t>0x304C</t>
+  </si>
+  <si>
+    <t>0x304D</t>
+  </si>
+  <si>
+    <t>0x304E</t>
+  </si>
+  <si>
+    <t>0x304F</t>
+  </si>
+  <si>
+    <t>预留(字)</t>
+  </si>
+  <si>
+    <t>speed_level(1字[1-4])</t>
+  </si>
+  <si>
+    <t>0x5128</t>
+  </si>
+  <si>
+    <t>0x0="OFF"；
+0x1="HEATING"；
+0x2="HOLDING"；
+0x3="COOLING"；
+0x4="UNKNOWN"</t>
+  </si>
+  <si>
+    <t>0x00="NORMAL"；
+0x01="LOW_WARNING"；
+0x02="EMPTY"；
+0x03="DRY_BURN"</t>
+  </si>
+  <si>
+    <t>0x00=false；0x01=true</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x1=2h,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+0x2=4h,
+0x3=8h,
+0x4=12h,</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x1=0.5h,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+0x2=1h,
+0x3=2h,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x1=2h,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+0x2=4h,
+0x3=6h,
+0x4=8h,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
       <t>0x1=15min；</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-</t>
+0x2=30min；
+0x3=60min；</t>
     </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>0x2=30min；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x3=60min；</t>
-    </r>
-  </si>
-  <si>
-    <t>screen_mode</t>
-  </si>
-  <si>
-    <t>0x3003</t>
-  </si>
-  <si>
-    <t>1=屏保，2=息屏</t>
-  </si>
-  <si>
-    <t>volume_percent</t>
-  </si>
-  <si>
-    <t>0x3004</t>
-  </si>
-  <si>
-    <t>language</t>
-  </si>
-  <si>
-    <t>0x3005</t>
-  </si>
-  <si>
-    <t>1=中；2=英；3=韩；4=日</t>
-  </si>
-  <si>
-    <t>local_password_enabled</t>
-  </si>
-  <si>
-    <t>0x3006</t>
-  </si>
-  <si>
-    <t>0x3007</t>
-  </si>
-  <si>
-    <t>0x3008</t>
-  </si>
-  <si>
-    <t>0x3009</t>
-  </si>
-  <si>
-    <t>0x300A</t>
-  </si>
-  <si>
-    <t>0x300B</t>
-  </si>
-  <si>
-    <t>0x300C</t>
-  </si>
-  <si>
-    <t>0x300D</t>
-  </si>
-  <si>
-    <t>0x300E-0x300F</t>
-  </si>
-  <si>
-    <t>temperature</t>
-  </si>
-  <si>
-    <t>0x3010-0x3011</t>
-  </si>
-  <si>
-    <t>double(4字节)</t>
-  </si>
-  <si>
-    <t>humidity</t>
-  </si>
-  <si>
-    <t>0x3012</t>
-  </si>
-  <si>
-    <t>pm25</t>
-  </si>
-  <si>
-    <t>0x3013-0x3014</t>
-  </si>
-  <si>
-    <t>co2</t>
-  </si>
-  <si>
-    <t>0x3015-0x3016</t>
-  </si>
-  <si>
-    <t>0x3017</t>
-  </si>
-  <si>
-    <t>door_status</t>
-  </si>
-  <si>
-    <t>0x3018</t>
-  </si>
-  <si>
-    <t>0x00=CLOSED；0x01=OPEN</t>
-  </si>
-  <si>
-    <t>lock_status</t>
-  </si>
-  <si>
-    <t>0x3019</t>
-  </si>
-  <si>
-    <t>0x00=LOCKED；0x01=UNLOCKED</t>
-  </si>
-  <si>
-    <t>exhaust-enabled</t>
-  </si>
-  <si>
-    <t>0x301A</t>
-  </si>
-  <si>
-    <t>0x00=false；0x01=true</t>
-  </si>
-  <si>
-    <t>exhaust-speed_level</t>
-  </si>
-  <si>
-    <t>0x301B</t>
-  </si>
-  <si>
-    <t>0x1，0x2，0x3，0x4，0x5，0x6</t>
-  </si>
-  <si>
-    <t>exhaust-interval_hours</t>
-  </si>
-  <si>
-    <t>0x301C</t>
-  </si>
-  <si>
-    <r>
       <t>0x1=0.5h,</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-</t>
+0x2=1h,
+0x3=2h,
+0x4=4h,
+0x5=8h,</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x2=1h,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x3=2h,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x4=4h,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x5=8h,</t>
-    </r>
-  </si>
-  <si>
-    <t>exhaust-running</t>
-  </si>
-  <si>
-    <t>0x301D</t>
-  </si>
-  <si>
-    <t>null</t>
-  </si>
-  <si>
-    <t>0x301E</t>
-  </si>
-  <si>
-    <t>light-enabled</t>
-  </si>
-  <si>
-    <t>0x301F</t>
-  </si>
-  <si>
-    <t>light-brightness_level</t>
-  </si>
-  <si>
-    <t>0x3020</t>
-  </si>
-  <si>
-    <t>0x1，0x2，0x3，0x4</t>
-  </si>
-  <si>
-    <t>light-running</t>
-  </si>
-  <si>
-    <t>0x3021</t>
-  </si>
-  <si>
-    <t>0x3022</t>
-  </si>
-  <si>
-    <t>0x3023</t>
-  </si>
-  <si>
-    <t>uvb-enabled</t>
-  </si>
-  <si>
-    <t>0x3024</t>
-  </si>
-  <si>
-    <t>uvb-level</t>
-  </si>
-  <si>
-    <t>0x3025</t>
-  </si>
-  <si>
-    <t>uvb-daily_hours</t>
-  </si>
-  <si>
-    <t>0x3026</t>
-  </si>
-  <si>
-    <r>
-      <t>0x1=2h,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x2=4h,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x3=6h,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x4=8h,</t>
-    </r>
-  </si>
-  <si>
-    <t>uvb-running</t>
-  </si>
-  <si>
-    <t>0x3027</t>
-  </si>
-  <si>
-    <t>uvb-null</t>
-  </si>
-  <si>
-    <t>0x3028</t>
-  </si>
-  <si>
-    <t>anion-enabled</t>
-  </si>
-  <si>
-    <t>0x3029</t>
-  </si>
-  <si>
-    <t>anion-running</t>
-  </si>
-  <si>
-    <t>0x302A</t>
-  </si>
-  <si>
-    <t>anion</t>
-  </si>
-  <si>
-    <t>0x302B</t>
-  </si>
-  <si>
-    <t>0x302C</t>
-  </si>
-  <si>
-    <t>0x302D</t>
-  </si>
-  <si>
-    <t>plasma-enabled</t>
-  </si>
-  <si>
-    <t>0x302E</t>
-  </si>
-  <si>
-    <t>plasma-running</t>
-  </si>
-  <si>
-    <t>0x302F</t>
-  </si>
-  <si>
-    <t>plasma</t>
-  </si>
-  <si>
-    <t>0x3030</t>
-  </si>
-  <si>
-    <t>0x3031</t>
-  </si>
-  <si>
-    <t>0x3032</t>
-  </si>
-  <si>
-    <t>climate-enabled</t>
-  </si>
-  <si>
-    <t>0x3033</t>
-  </si>
-  <si>
-    <t>climate-target_celsius</t>
-  </si>
-  <si>
-    <t>0x3034</t>
-  </si>
-  <si>
-    <t>20-35</t>
-  </si>
-  <si>
-    <t>climate-control_status</t>
-  </si>
-  <si>
-    <t>0x3035</t>
-  </si>
-  <si>
-    <t>0x0=“?”；0x1=“HEATING”</t>
-  </si>
-  <si>
-    <t>climate-running</t>
-  </si>
-  <si>
-    <t>0x3036</t>
-  </si>
-  <si>
-    <t>climate</t>
-  </si>
-  <si>
-    <t>0x3037</t>
-  </si>
-  <si>
-    <t>humidifier-enabled</t>
-  </si>
-  <si>
-    <t>0x3038</t>
-  </si>
-  <si>
-    <t>humidifier-interval_hours</t>
-  </si>
-  <si>
-    <t>0x3039</t>
-  </si>
-  <si>
-    <r>
-      <t>0x1=2h,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x2=4h,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x3=8h,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x4=12h,</t>
-    </r>
-  </si>
-  <si>
-    <t>humidifier-running_hours</t>
-  </si>
-  <si>
-    <t>0x303A</t>
-  </si>
-  <si>
-    <r>
-      <t>0x1=0.5h,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x2=1h,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0x3=2h,</t>
-    </r>
-  </si>
-  <si>
-    <t>humidifier-running</t>
-  </si>
-  <si>
-    <t>0x303B</t>
-  </si>
-  <si>
-    <t>humidifier-liquid_status</t>
-  </si>
-  <si>
-    <t>0x303C</t>
-  </si>
-  <si>
-    <t>0x00="NORMAL";</t>
-  </si>
-  <si>
-    <t>inlet_fan-enabled</t>
-  </si>
-  <si>
-    <t>0x303D</t>
-  </si>
-  <si>
-    <t>inlet_fan-speed_level</t>
-  </si>
-  <si>
-    <t>0x303E</t>
-  </si>
-  <si>
-    <t>0x1,0x2,0x3,0x4</t>
-  </si>
-  <si>
-    <t>inlet_fan-running</t>
-  </si>
-  <si>
-    <t>0x303F</t>
-  </si>
-  <si>
-    <t>inlet_fan-</t>
-  </si>
-  <si>
-    <t>0x3040</t>
-  </si>
-  <si>
-    <t>0x3041</t>
-  </si>
-  <si>
-    <t>filter-life_percent</t>
-  </si>
-  <si>
-    <t>0x3042</t>
-  </si>
-  <si>
-    <t>filter-need_replace</t>
-  </si>
-  <si>
-    <t>0x3043</t>
-  </si>
-  <si>
-    <t>filter-</t>
-  </si>
-  <si>
-    <t>0x3044</t>
-  </si>
-  <si>
-    <t>0x3045</t>
-  </si>
-  <si>
-    <t>0x3046</t>
-  </si>
-  <si>
-    <t>0x3047</t>
-  </si>
-  <si>
-    <t>0x3048</t>
-  </si>
-  <si>
-    <t>0x3049</t>
-  </si>
-  <si>
-    <t>0x304A</t>
-  </si>
-  <si>
-    <t>0x304B</t>
-  </si>
-  <si>
-    <t>0x304C</t>
-  </si>
-  <si>
-    <t>0x304D</t>
-  </si>
-  <si>
-    <t>0x304E</t>
-  </si>
-  <si>
-    <t>0x304F</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -897,44 +749,38 @@
       <color rgb="FFFE0300"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -942,15 +788,12 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -958,30 +801,25 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -989,22 +827,19 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1012,36 +847,64 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="37">
@@ -1054,211 +917,194 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7DCE5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCC102"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.59996337778862885"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.59996337778862885"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.59996337778862885"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.59996337778862885"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.59996337778862885"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.59996337778862885"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1290,7 +1136,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49995422223578601"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1373,7 +1219,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1382,10 +1228,10 @@
     <xf numFmtId="0" fontId="13" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1394,7 +1240,7 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1403,13 +1249,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1518,7 +1364,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1557,9 +1403,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1569,62 +1412,72 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
+    <cellStyle name="百分比" xfId="11"/>
+    <cellStyle name="标题" xfId="17"/>
+    <cellStyle name="标题 1" xfId="19"/>
+    <cellStyle name="标题 2" xfId="20"/>
+    <cellStyle name="标题 3" xfId="22"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="差" xfId="7"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="10"/>
+    <cellStyle name="好" xfId="31"/>
+    <cellStyle name="汇总" xfId="30"/>
+    <cellStyle name="货币" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="1"/>
+    <cellStyle name="计算" xfId="25"/>
+    <cellStyle name="检查单元格" xfId="26"/>
+    <cellStyle name="解释性文本" xfId="18"/>
+    <cellStyle name="警告文本" xfId="16"/>
+    <cellStyle name="链接单元格" xfId="29"/>
+    <cellStyle name="千位分隔" xfId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="5"/>
+    <cellStyle name="强调文字颜色 1" xfId="34"/>
+    <cellStyle name="强调文字颜色 2" xfId="28"/>
+    <cellStyle name="强调文字颜色 3" xfId="39"/>
+    <cellStyle name="强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="43"/>
+    <cellStyle name="强调文字颜色 6" xfId="46"/>
+    <cellStyle name="适中" xfId="32"/>
+    <cellStyle name="输出" xfId="24"/>
+    <cellStyle name="输入" xfId="3"/>
+    <cellStyle name="已访问的超链接" xfId="12"/>
+    <cellStyle name="注释" xfId="13"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1674,73 +1527,13 @@
     <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1752,23 +1545,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1778,23 +1571,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1802,26 +1595,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1856,17 +1646,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1882,16 +1672,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AN210"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="53.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:40">
+    <row r="1" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1899,271 +1693,271 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+    </row>
+    <row r="2" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16"/>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16"/>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16"/>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16"/>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16"/>
-      <c r="AK1" s="16"/>
-      <c r="AL1" s="16"/>
-      <c r="AM1" s="16"/>
-      <c r="AN1" s="16"/>
-    </row>
-    <row r="2" ht="14.25" spans="1:8">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>8</v>
       </c>
       <c r="C2" s="7">
         <v>4</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>11</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" ht="14.25" spans="1:8">
+    <row r="3" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="C3" s="7">
         <v>4</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" ht="14.25" spans="1:8">
+    <row r="4" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="C4" s="7">
         <v>4</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" ht="14.25" spans="1:8">
+    <row r="5" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="C5" s="7">
         <v>4</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" ht="14.25" spans="1:8">
+    <row r="6" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="C6" s="7">
         <v>4</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" ht="14.25" spans="1:8">
+    <row r="7" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="C7" s="7">
         <v>4</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" ht="14.25" spans="1:8">
+    <row r="8" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="C8" s="7">
         <v>4</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" ht="14.25" spans="1:8">
+    <row r="9" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="C9" s="7">
         <v>4</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" ht="14.25" spans="1:8">
+    <row r="10" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="C10" s="7">
         <v>4</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
     </row>
-    <row r="11" ht="14.25" spans="1:8">
+    <row r="11" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="C11" s="7">
         <v>4</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" ht="14.25" spans="1:8">
+    <row r="12" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="C12" s="7">
         <v>4</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" ht="14.25" spans="1:8">
+    <row r="13" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
@@ -2173,12 +1967,12 @@
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" ht="14.25" spans="1:8">
+    <row r="14" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="7">
         <v>1</v>
@@ -2189,12 +1983,12 @@
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
     </row>
-    <row r="15" ht="14.25" spans="1:8">
+    <row r="15" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -2205,18 +1999,18 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" ht="14.25" spans="5:8">
+    <row r="16" spans="1:40" ht="14.25" x14ac:dyDescent="0.2">
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" ht="14.25" spans="1:8">
+    <row r="17" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" s="7">
         <v>64</v>
@@ -2227,7 +2021,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" ht="14.25" spans="1:8">
+    <row r="18" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
@@ -2237,7 +2031,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" ht="14.25" spans="1:8">
+    <row r="19" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
@@ -2247,9 +2041,9 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" ht="14.25" spans="1:7">
+    <row r="20" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="7"/>
@@ -2258,119 +2052,119 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" ht="14.25" spans="1:8">
+    <row r="21" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="D21" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" ht="14.25" spans="1:8">
+    <row r="22" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>51</v>
-      </c>
       <c r="D22" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
     </row>
-    <row r="23" ht="14.25" spans="1:7">
+    <row r="23" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>190</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" ht="14.25" spans="1:8">
+    <row r="24" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
     </row>
-    <row r="25" ht="14.25" spans="1:8">
+    <row r="25" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
     </row>
-    <row r="26" ht="14.25" spans="1:8">
+    <row r="26" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
     </row>
-    <row r="27" ht="14.25" spans="1:8">
+    <row r="27" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="8"/>
@@ -2379,10 +2173,10 @@
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" ht="14.25" spans="1:8">
+    <row r="28" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
       <c r="B28" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="8"/>
@@ -2391,10 +2185,10 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" ht="14.25" spans="1:8">
+    <row r="29" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A29" s="5"/>
       <c r="B29" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="8"/>
@@ -2403,10 +2197,10 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" ht="14.25" spans="1:8">
+    <row r="30" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A30" s="5"/>
       <c r="B30" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="8"/>
@@ -2415,10 +2209,10 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" ht="14.25" spans="1:8">
+    <row r="31" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
       <c r="B31" s="9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="8"/>
@@ -2427,10 +2221,10 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" ht="14.25" spans="1:7">
+    <row r="32" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A32" s="5"/>
       <c r="B32" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="8"/>
@@ -2438,10 +2232,10 @@
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
     </row>
-    <row r="33" ht="14.25" spans="1:7">
+    <row r="33" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A33" s="5"/>
       <c r="B33" s="9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="8"/>
@@ -2449,10 +2243,10 @@
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
     </row>
-    <row r="34" ht="14.25" spans="1:7">
+    <row r="34" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A34" s="5"/>
       <c r="B34" s="9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="8"/>
@@ -2460,10 +2254,10 @@
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
     </row>
-    <row r="35" ht="14.25" spans="1:7">
+    <row r="35" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="8"/>
@@ -2471,44 +2265,44 @@
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
     </row>
-    <row r="36" ht="14.25" spans="1:7">
+    <row r="36" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
     </row>
-    <row r="37" ht="14.25" spans="1:7">
+    <row r="37" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
     </row>
-    <row r="38" ht="14.25" spans="1:7">
+    <row r="38" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="8"/>
@@ -2516,12 +2310,12 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
     </row>
-    <row r="39" ht="14.25" spans="1:7">
+    <row r="39" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="8"/>
@@ -2529,10 +2323,10 @@
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
     </row>
-    <row r="40" ht="14.25" spans="1:7">
+    <row r="40" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A40" s="11"/>
       <c r="B40" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="8"/>
@@ -2540,180 +2334,180 @@
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
     </row>
-    <row r="41" ht="14.25" spans="1:7">
+    <row r="41" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
     </row>
-    <row r="42" ht="14.25" spans="1:7">
+    <row r="42" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
     </row>
-    <row r="43" ht="14.25" spans="1:7">
+    <row r="43" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A43" s="13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
     </row>
-    <row r="44" ht="14.25" spans="1:7">
+    <row r="44" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A44" s="13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
     </row>
-    <row r="45" ht="71.25" spans="1:7">
+    <row r="45" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>97</v>
+        <v>93</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>191</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
     </row>
-    <row r="46" ht="14.25" spans="1:7">
+    <row r="46" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
     </row>
-    <row r="47" ht="14.25" spans="1:7">
+    <row r="47" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A47" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
     </row>
-    <row r="48" ht="14.25" spans="1:7">
-      <c r="A48" s="15" t="s">
-        <v>102</v>
+    <row r="48" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A48" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
     </row>
-    <row r="49" ht="14.25" spans="1:7">
-      <c r="A49" s="15" t="s">
-        <v>104</v>
+    <row r="49" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A49" s="14" t="s">
+        <v>100</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
     </row>
-    <row r="50" ht="14.25" spans="1:7">
-      <c r="A50" s="15" t="s">
-        <v>107</v>
+    <row r="50" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A50" s="14" t="s">
+        <v>103</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
     </row>
-    <row r="51" ht="14.25" spans="1:7">
-      <c r="A51" s="15" t="s">
-        <v>100</v>
+    <row r="51" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A51" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="8"/>
@@ -2721,12 +2515,12 @@
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
     </row>
-    <row r="52" ht="14.25" spans="1:7">
-      <c r="A52" s="15" t="s">
-        <v>100</v>
+    <row r="52" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A52" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="8"/>
@@ -2734,80 +2528,80 @@
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
     </row>
-    <row r="53" ht="14.25" spans="1:7">
+    <row r="53" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A53" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
     </row>
-    <row r="54" ht="14.25" spans="1:7">
+    <row r="54" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A54" s="13" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
     </row>
-    <row r="55" ht="57" spans="1:7">
+    <row r="55" spans="1:7" ht="57" x14ac:dyDescent="0.2">
       <c r="A55" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>117</v>
+        <v>112</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>189</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" ht="14.25" spans="1:7">
+    <row r="56" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A56" s="13" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" ht="14.25" spans="1:7">
+    <row r="57" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A57" s="13" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="8"/>
@@ -2815,46 +2609,46 @@
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" ht="14.25" spans="1:7">
-      <c r="A58" s="15" t="s">
-        <v>122</v>
+    <row r="58" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A58" s="14" t="s">
+        <v>117</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" ht="14.25" spans="1:7">
-      <c r="A59" s="15" t="s">
-        <v>124</v>
+    <row r="59" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A59" s="14" t="s">
+        <v>119</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" ht="14.25" spans="1:7">
-      <c r="A60" s="15" t="s">
-        <v>126</v>
+    <row r="60" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A60" s="14" t="s">
+        <v>121</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="8"/>
@@ -2862,12 +2656,12 @@
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
     </row>
-    <row r="61" ht="14.25" spans="1:7">
-      <c r="A61" s="15" t="s">
-        <v>126</v>
+    <row r="61" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A61" s="14" t="s">
+        <v>121</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="8"/>
@@ -2875,12 +2669,12 @@
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
     </row>
-    <row r="62" ht="14.25" spans="1:7">
-      <c r="A62" s="15" t="s">
-        <v>126</v>
+    <row r="62" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A62" s="14" t="s">
+        <v>121</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="8"/>
@@ -2888,46 +2682,46 @@
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
     </row>
-    <row r="63" ht="14.25" spans="1:7">
+    <row r="63" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A63" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
       <c r="G63" s="8"/>
     </row>
-    <row r="64" ht="14.25" spans="1:7">
+    <row r="64" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A64" s="13" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
     </row>
-    <row r="65" ht="14.25" spans="1:7">
+    <row r="65" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A65" s="13" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="8"/>
@@ -2935,12 +2729,12 @@
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
     </row>
-    <row r="66" ht="14.25" spans="1:7">
+    <row r="66" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A66" s="13" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="8"/>
@@ -2948,12 +2742,12 @@
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
     </row>
-    <row r="67" ht="14.25" spans="1:7">
+    <row r="67" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A67" s="13" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="8"/>
@@ -2961,80 +2755,80 @@
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
     </row>
-    <row r="68" ht="14.25" spans="1:7">
-      <c r="A68" s="15" t="s">
-        <v>138</v>
+    <row r="68" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A68" s="14" t="s">
+        <v>133</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
     </row>
-    <row r="69" ht="14.25" spans="1:7">
-      <c r="A69" s="15" t="s">
-        <v>140</v>
+    <row r="69" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A69" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
     </row>
-    <row r="70" ht="14.25" spans="1:7">
-      <c r="A70" s="15" t="s">
-        <v>143</v>
+    <row r="70" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="14" t="s">
+        <v>138</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
     </row>
-    <row r="71" ht="14.25" spans="1:7">
-      <c r="A71" s="15" t="s">
-        <v>146</v>
+    <row r="71" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A71" s="14" t="s">
+        <v>140</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
     </row>
-    <row r="72" ht="14.25" spans="1:7">
-      <c r="A72" s="15" t="s">
-        <v>148</v>
+    <row r="72" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A72" s="14" t="s">
+        <v>142</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C72" s="7"/>
       <c r="D72" s="8"/>
@@ -3042,148 +2836,147 @@
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
     </row>
-    <row r="73" ht="14.25" spans="1:7">
+    <row r="73" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A73" s="13" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
     </row>
-    <row r="74" ht="57" spans="1:7">
+    <row r="74" spans="1:7" ht="57" x14ac:dyDescent="0.2">
       <c r="A74" s="13" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>154</v>
+        <v>147</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>187</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
       <c r="G74" s="8"/>
     </row>
-    <row r="75" ht="42.75" spans="1:7">
+    <row r="75" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A75" s="13" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>157</v>
+        <v>149</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>188</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E75"/>
+        <v>46</v>
+      </c>
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
     </row>
-    <row r="76" ht="14.25" spans="1:7">
+    <row r="76" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A76" s="13" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
     </row>
-    <row r="77" ht="14.25" spans="1:7">
+    <row r="77" spans="1:7" ht="52.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="13" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
     </row>
-    <row r="78" ht="14.25" spans="1:7">
-      <c r="A78" s="15" t="s">
-        <v>163</v>
+    <row r="78" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A78" s="14" t="s">
+        <v>154</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
     </row>
-    <row r="79" ht="14.25" spans="1:7">
-      <c r="A79" s="15" t="s">
-        <v>165</v>
+    <row r="79" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A79" s="14" t="s">
+        <v>156</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
     </row>
-    <row r="80" ht="14.25" spans="1:7">
-      <c r="A80" s="15" t="s">
-        <v>168</v>
+    <row r="80" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A80" s="14" t="s">
+        <v>159</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
     </row>
-    <row r="81" ht="14.25" spans="1:7">
-      <c r="A81" s="15" t="s">
-        <v>170</v>
+    <row r="81" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A81" s="14" t="s">
+        <v>161</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C81" s="7"/>
       <c r="D81" s="8"/>
@@ -3191,12 +2984,12 @@
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
     </row>
-    <row r="82" ht="14.25" spans="1:7">
-      <c r="A82" s="15" t="s">
-        <v>170</v>
+    <row r="82" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A82" s="14" t="s">
+        <v>161</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C82" s="7"/>
       <c r="D82" s="8"/>
@@ -3204,46 +2997,46 @@
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
     </row>
-    <row r="83" ht="14.25" spans="1:7">
+    <row r="83" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A83" s="13" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
     </row>
-    <row r="84" ht="14.25" spans="1:7">
+    <row r="84" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A84" s="13" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
     </row>
-    <row r="85" ht="14.25" spans="1:7">
+    <row r="85" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A85" s="13" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C85" s="7"/>
       <c r="D85" s="8"/>
@@ -3251,12 +3044,12 @@
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
     </row>
-    <row r="86" ht="14.25" spans="1:7">
+    <row r="86" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A86" s="13" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C86" s="7"/>
       <c r="D86" s="8"/>
@@ -3264,12 +3057,12 @@
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
     </row>
-    <row r="87" ht="14.25" spans="1:7">
+    <row r="87" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A87" s="13" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C87" s="7"/>
       <c r="D87" s="8"/>
@@ -3277,10 +3070,10 @@
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
     </row>
-    <row r="88" ht="14.25" spans="1:7">
+    <row r="88" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A88" s="5"/>
       <c r="B88" s="9" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C88" s="7"/>
       <c r="D88" s="8"/>
@@ -3288,10 +3081,10 @@
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
     </row>
-    <row r="89" ht="14.25" spans="1:7">
+    <row r="89" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A89" s="5"/>
       <c r="B89" s="9" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C89" s="7"/>
       <c r="D89" s="8"/>
@@ -3299,10 +3092,10 @@
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
     </row>
-    <row r="90" ht="14.25" spans="1:7">
+    <row r="90" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A90" s="5"/>
       <c r="B90" s="9" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C90" s="7"/>
       <c r="D90" s="8"/>
@@ -3310,10 +3103,10 @@
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
     </row>
-    <row r="91" ht="14.25" spans="1:7">
+    <row r="91" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A91" s="5"/>
       <c r="B91" s="9" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="8"/>
@@ -3321,10 +3114,10 @@
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
     </row>
-    <row r="92" ht="14.25" spans="1:7">
+    <row r="92" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A92" s="5"/>
       <c r="B92" s="9" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="8"/>
@@ -3332,10 +3125,10 @@
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
     </row>
-    <row r="93" ht="14.25" spans="1:7">
+    <row r="93" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A93" s="5"/>
       <c r="B93" s="9" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="8"/>
@@ -3343,10 +3136,10 @@
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
     </row>
-    <row r="94" ht="14.25" spans="1:7">
+    <row r="94" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A94" s="5"/>
       <c r="B94" s="9" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="8"/>
@@ -3354,10 +3147,10 @@
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
     </row>
-    <row r="95" ht="14.25" spans="1:7">
+    <row r="95" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A95" s="5"/>
       <c r="B95" s="9" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="8"/>
@@ -3365,10 +3158,10 @@
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
     </row>
-    <row r="96" ht="14.25" spans="1:7">
+    <row r="96" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A96" s="5"/>
       <c r="B96" s="9" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="8"/>
@@ -3376,350 +3169,351 @@
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
     </row>
-    <row r="97" spans="2:2">
-      <c r="B97" s="17"/>
-    </row>
-    <row r="98" spans="2:2">
-      <c r="B98" s="17"/>
-    </row>
-    <row r="99" spans="2:2">
-      <c r="B99" s="17"/>
-    </row>
-    <row r="100" spans="2:2">
-      <c r="B100" s="17"/>
-    </row>
-    <row r="101" spans="2:2">
-      <c r="B101" s="17"/>
-    </row>
-    <row r="102" spans="2:2">
-      <c r="B102" s="17"/>
-    </row>
-    <row r="103" spans="2:2">
-      <c r="B103" s="17"/>
-    </row>
-    <row r="104" spans="2:2">
-      <c r="B104" s="17"/>
-    </row>
-    <row r="105" spans="2:2">
-      <c r="B105" s="17"/>
-    </row>
-    <row r="106" spans="2:2">
-      <c r="B106" s="17"/>
-    </row>
-    <row r="107" spans="2:2">
-      <c r="B107" s="17"/>
-    </row>
-    <row r="108" spans="2:2">
-      <c r="B108" s="17"/>
-    </row>
-    <row r="109" spans="2:2">
-      <c r="B109" s="17"/>
-    </row>
-    <row r="110" spans="2:2">
-      <c r="B110" s="17"/>
-    </row>
-    <row r="111" spans="2:2">
-      <c r="B111" s="17"/>
-    </row>
-    <row r="112" spans="2:2">
-      <c r="B112" s="17"/>
-    </row>
-    <row r="113" spans="2:2">
-      <c r="B113" s="17"/>
-    </row>
-    <row r="114" spans="2:2">
-      <c r="B114" s="17"/>
-    </row>
-    <row r="115" spans="2:2">
-      <c r="B115" s="17"/>
-    </row>
-    <row r="116" spans="2:2">
-      <c r="B116" s="17"/>
-    </row>
-    <row r="117" spans="2:2">
-      <c r="B117" s="17"/>
-    </row>
-    <row r="118" spans="2:2">
-      <c r="B118" s="17"/>
-    </row>
-    <row r="119" spans="2:2">
-      <c r="B119" s="17"/>
-    </row>
-    <row r="120" spans="2:2">
-      <c r="B120" s="17"/>
-    </row>
-    <row r="121" spans="2:2">
-      <c r="B121" s="17"/>
-    </row>
-    <row r="122" spans="2:2">
-      <c r="B122" s="17"/>
-    </row>
-    <row r="123" spans="2:2">
-      <c r="B123" s="17"/>
-    </row>
-    <row r="124" spans="2:2">
-      <c r="B124" s="17"/>
-    </row>
-    <row r="125" spans="2:2">
-      <c r="B125" s="17"/>
-    </row>
-    <row r="126" spans="2:2">
-      <c r="B126" s="17"/>
-    </row>
-    <row r="127" spans="2:2">
-      <c r="B127" s="17"/>
-    </row>
-    <row r="128" spans="2:2">
-      <c r="B128" s="17"/>
-    </row>
-    <row r="129" spans="2:2">
-      <c r="B129" s="17"/>
-    </row>
-    <row r="130" spans="2:2">
-      <c r="B130" s="17"/>
-    </row>
-    <row r="131" spans="2:2">
-      <c r="B131" s="17"/>
-    </row>
-    <row r="132" spans="2:2">
-      <c r="B132" s="17"/>
-    </row>
-    <row r="133" spans="2:2">
-      <c r="B133" s="17"/>
-    </row>
-    <row r="134" spans="2:2">
-      <c r="B134" s="17"/>
-    </row>
-    <row r="135" spans="2:2">
-      <c r="B135" s="17"/>
-    </row>
-    <row r="136" spans="2:2">
-      <c r="B136" s="17"/>
-    </row>
-    <row r="137" spans="2:2">
-      <c r="B137" s="17"/>
-    </row>
-    <row r="138" spans="2:2">
-      <c r="B138" s="17"/>
-    </row>
-    <row r="139" spans="2:2">
-      <c r="B139" s="17"/>
-    </row>
-    <row r="140" spans="2:2">
-      <c r="B140" s="17"/>
-    </row>
-    <row r="141" spans="2:2">
-      <c r="B141" s="17"/>
-    </row>
-    <row r="142" spans="2:2">
-      <c r="B142" s="17"/>
-    </row>
-    <row r="143" spans="2:2">
-      <c r="B143" s="17"/>
-    </row>
-    <row r="144" spans="2:2">
-      <c r="B144" s="17"/>
-    </row>
-    <row r="145" spans="2:2">
-      <c r="B145" s="17"/>
-    </row>
-    <row r="146" spans="2:2">
-      <c r="B146" s="17"/>
-    </row>
-    <row r="147" spans="2:2">
-      <c r="B147" s="17"/>
-    </row>
-    <row r="148" spans="2:2">
-      <c r="B148" s="17"/>
-    </row>
-    <row r="149" spans="2:2">
-      <c r="B149" s="17"/>
-    </row>
-    <row r="150" spans="2:2">
-      <c r="B150" s="17"/>
-    </row>
-    <row r="151" spans="2:2">
-      <c r="B151" s="17"/>
-    </row>
-    <row r="152" spans="2:2">
-      <c r="B152" s="17"/>
-    </row>
-    <row r="153" spans="2:2">
-      <c r="B153" s="17"/>
-    </row>
-    <row r="154" spans="2:2">
-      <c r="B154" s="17"/>
-    </row>
-    <row r="155" spans="2:2">
-      <c r="B155" s="17"/>
-    </row>
-    <row r="156" spans="2:2">
-      <c r="B156" s="17"/>
-    </row>
-    <row r="157" spans="2:2">
-      <c r="B157" s="17"/>
-    </row>
-    <row r="158" spans="2:2">
-      <c r="B158" s="17"/>
-    </row>
-    <row r="159" spans="2:2">
-      <c r="B159" s="17"/>
-    </row>
-    <row r="160" spans="2:2">
-      <c r="B160" s="17"/>
-    </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="17"/>
-    </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="17"/>
-    </row>
-    <row r="163" spans="2:2">
-      <c r="B163" s="17"/>
-    </row>
-    <row r="164" spans="2:2">
-      <c r="B164" s="17"/>
-    </row>
-    <row r="165" spans="2:2">
-      <c r="B165" s="17"/>
-    </row>
-    <row r="166" spans="2:2">
-      <c r="B166" s="17"/>
-    </row>
-    <row r="167" spans="2:2">
-      <c r="B167" s="17"/>
-    </row>
-    <row r="168" spans="2:2">
-      <c r="B168" s="17"/>
-    </row>
-    <row r="169" spans="2:2">
-      <c r="B169" s="17"/>
-    </row>
-    <row r="170" spans="2:2">
-      <c r="B170" s="17"/>
-    </row>
-    <row r="171" spans="2:2">
-      <c r="B171" s="17"/>
-    </row>
-    <row r="172" spans="2:2">
-      <c r="B172" s="17"/>
-    </row>
-    <row r="173" spans="2:2">
-      <c r="B173" s="17"/>
-    </row>
-    <row r="174" spans="2:2">
-      <c r="B174" s="17"/>
-    </row>
-    <row r="175" spans="2:2">
-      <c r="B175" s="17"/>
-    </row>
-    <row r="176" spans="2:2">
-      <c r="B176" s="17"/>
-    </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="17"/>
-    </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="17"/>
-    </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="17"/>
-    </row>
-    <row r="180" spans="2:2">
-      <c r="B180" s="17"/>
-    </row>
-    <row r="181" spans="2:2">
-      <c r="B181" s="17"/>
-    </row>
-    <row r="182" spans="2:2">
-      <c r="B182" s="17"/>
-    </row>
-    <row r="183" spans="2:2">
-      <c r="B183" s="17"/>
-    </row>
-    <row r="184" spans="2:2">
-      <c r="B184" s="17"/>
-    </row>
-    <row r="185" spans="2:2">
-      <c r="B185" s="17"/>
-    </row>
-    <row r="186" spans="2:2">
-      <c r="B186" s="17"/>
-    </row>
-    <row r="187" spans="2:2">
-      <c r="B187" s="17"/>
-    </row>
-    <row r="188" spans="2:2">
-      <c r="B188" s="17"/>
-    </row>
-    <row r="189" spans="2:2">
-      <c r="B189" s="17"/>
-    </row>
-    <row r="190" spans="2:2">
-      <c r="B190" s="17"/>
-    </row>
-    <row r="191" spans="2:2">
-      <c r="B191" s="17"/>
-    </row>
-    <row r="192" spans="2:2">
-      <c r="B192" s="17"/>
-    </row>
-    <row r="193" spans="2:2">
-      <c r="B193" s="17"/>
-    </row>
-    <row r="194" spans="2:2">
-      <c r="B194" s="17"/>
-    </row>
-    <row r="195" spans="2:2">
-      <c r="B195" s="17"/>
-    </row>
-    <row r="196" spans="2:2">
-      <c r="B196" s="17"/>
-    </row>
-    <row r="197" spans="2:2">
-      <c r="B197" s="17"/>
-    </row>
-    <row r="198" spans="2:2">
-      <c r="B198" s="17"/>
-    </row>
-    <row r="199" spans="2:2">
-      <c r="B199" s="17"/>
-    </row>
-    <row r="200" spans="2:2">
-      <c r="B200" s="17"/>
-    </row>
-    <row r="201" spans="2:2">
-      <c r="B201" s="17"/>
-    </row>
-    <row r="202" spans="2:2">
-      <c r="B202" s="17"/>
-    </row>
-    <row r="203" spans="2:2">
-      <c r="B203" s="17"/>
-    </row>
-    <row r="204" spans="2:2">
-      <c r="B204" s="17"/>
-    </row>
-    <row r="205" spans="2:2">
-      <c r="B205" s="17"/>
-    </row>
-    <row r="206" spans="2:2">
-      <c r="B206" s="17"/>
-    </row>
-    <row r="207" spans="2:2">
-      <c r="B207" s="17"/>
-    </row>
-    <row r="208" spans="2:2">
-      <c r="B208" s="17"/>
-    </row>
-    <row r="209" spans="2:2">
-      <c r="B209" s="17"/>
-    </row>
-    <row r="210" spans="2:2">
-      <c r="B210" s="17"/>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B97" s="16"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B98" s="16"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B99" s="16"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B100" s="16"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B101" s="16"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B102" s="16"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B103" s="16"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B104" s="16"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B105" s="16"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B106" s="16"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B107" s="16"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B108" s="16"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B109" s="16"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B110" s="16"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B111" s="16"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B112" s="16"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B113" s="16"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B114" s="16"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B115" s="16"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B116" s="16"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B117" s="16"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B118" s="16"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B119" s="16"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B120" s="16"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B121" s="16"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B122" s="16"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B123" s="16"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B124" s="16"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B125" s="16"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B126" s="16"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B127" s="16"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B128" s="16"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B129" s="16"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B130" s="16"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B131" s="16"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B132" s="16"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B133" s="16"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B134" s="16"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B135" s="16"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B136" s="16"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B137" s="16"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B138" s="16"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B139" s="16"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B140" s="16"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B141" s="16"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B142" s="16"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B143" s="16"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B144" s="16"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B145" s="16"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B146" s="16"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B147" s="16"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B148" s="16"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B149" s="16"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B150" s="16"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B151" s="16"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B152" s="16"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B153" s="16"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B154" s="16"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B155" s="16"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B156" s="16"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B157" s="16"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B158" s="16"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B159" s="16"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B160" s="16"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B161" s="16"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B162" s="16"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B163" s="16"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B164" s="16"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B165" s="16"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B166" s="16"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B167" s="16"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B168" s="16"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B169" s="16"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B170" s="16"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B171" s="16"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B172" s="16"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B173" s="16"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B174" s="16"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B175" s="16"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B176" s="16"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B177" s="16"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B178" s="16"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B179" s="16"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B180" s="16"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B181" s="16"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B182" s="16"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B183" s="16"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B184" s="16"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B185" s="16"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B186" s="16"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B187" s="16"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B188" s="16"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B189" s="16"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B190" s="16"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B191" s="16"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B192" s="16"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B193" s="16"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B194" s="16"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B195" s="16"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B196" s="16"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B197" s="16"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B198" s="16"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B199" s="16"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B200" s="16"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B201" s="16"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B202" s="16"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B203" s="16"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B204" s="16"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B205" s="16"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B206" s="16"/>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B207" s="16"/>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B208" s="16"/>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B209" s="16"/>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B210" s="16"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <phoneticPr fontId="24" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>